--- a/output/pdf_financials_xlsx/BIOV.xlsx
+++ b/output/pdf_financials_xlsx/BIOV.xlsx
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.781146</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.939147</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.270629</v>
       </c>
     </row>
     <row r="93">
@@ -3108,7 +3108,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3496,7 +3500,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>1.781146</v>
       </c>

--- a/output/pdf_financials_xlsx/BIOV.xlsx
+++ b/output/pdf_financials_xlsx/BIOV.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.141898</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000977</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.211806</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.141898</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000977</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.211806</v>
       </c>
     </row>
     <row r="37">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.5634940000000001</v>
+        <v>0.421596</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.113478</v>
+        <v>0.112501</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
